--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="53">
   <si>
     <t>_reportFile</t>
   </si>
@@ -106,7 +106,7 @@
     <t>index</t>
   </si>
   <si>
-    <t>2026-08-13T18:37:56.910Z</t>
+    <t>2026-08-13T19:09:49.009Z</t>
   </si>
   <si>
     <t>http://localhost:8082/</t>
@@ -155,6 +155,27 @@
   </si>
   <si>
     <t>http://localhost:8082/lsa/prospective-students.html</t>
+  </si>
+  <si>
+    <t>lsa/academics/majors-minors.report.json</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>lsa/academics/majors-minors</t>
+  </si>
+  <si>
+    <t>academics-listing</t>
+  </si>
+  <si>
+    <t>2026-08-13T18:48:55.438Z</t>
+  </si>
+  <si>
+    <t>Majors and Minors | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>http://localhost:8082/lsa/academics/majors-minors.html</t>
   </si>
 </sst>
 </file>
@@ -543,14 +564,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="39" customWidth="1"/>
+    <col min="1" max="1" width="41" customWidth="1"/>
     <col min="2" max="4" width="50" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="27" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="6" max="6" width="29" customWidth="1"/>
+    <col min="8" max="8" width="19" customWidth="1"/>
     <col min="9" max="9" width="26" customWidth="1"/>
     <col min="10" max="11" width="50" customWidth="1"/>
   </cols>
@@ -800,6 +821,41 @@
         <v>45</v>
       </c>
     </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" t="s">
+        <v>50</v>
+      </c>
+      <c r="J8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K8" t="s">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
